--- a/Stock_OneClick/history/scan_result_20260529_104654.xlsx
+++ b/Stock_OneClick/history/scan_result_20260529_104654.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -637,24 +637,12 @@
       <c r="J3" s="4" t="n">
         <v>170.18</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-29; 相对D0=1.68%; 本次触发=2026-05-29(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -706,24 +694,12 @@
       <c r="J4" s="4" t="n">
         <v>193.7164</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-29; 相对D0=7.58%; 本次触发=2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -775,24 +751,12 @@
       <c r="J5" s="4" t="n">
         <v>48.22</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-29; 相对D0=0.21%; 本次触发=2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -844,24 +808,12 @@
       <c r="J6" s="4" t="n">
         <v>13.825</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-29; 相对D0=6.18%; 本次触发=2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -913,24 +865,6 @@
       <c r="J7" t="n">
         <v>89.17</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-05-29; 相对D0=0.76%; 本次触发=2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -982,24 +916,6 @@
       <c r="J8" t="n">
         <v>161.6701</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-05-29; 相对D0=2.10%; 本次触发=2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1051,27 +967,15 @@
       <c r="J9" s="4" t="n">
         <v>257.85</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>D0=257.85; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=257.85; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1024,12 @@
       <c r="J10" s="4" t="n">
         <v>287.31</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>D0=287.31; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式买入)</t>
@@ -1189,24 +1081,12 @@
       <c r="J11" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=216.00; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(预警买入)</t>
@@ -1258,24 +1138,6 @@
       <c r="J12" t="n">
         <v>153.78</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-29; 相对D0=-15.27%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -1327,24 +1189,12 @@
       <c r="J13" s="4" t="n">
         <v>196.9875</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-29; 相对D0=-2.92%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1396,24 +1246,12 @@
       <c r="J14" s="4" t="n">
         <v>52.44</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-29; 相对D0=12.70%</t>
@@ -1465,24 +1303,6 @@
       <c r="J15" t="n">
         <v>16.62</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-29; 相对D0=3.10%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -1534,24 +1354,6 @@
       <c r="J16" t="n">
         <v>132.98</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-29; 相对D0=-5.83%</t>
@@ -1603,24 +1405,6 @@
       <c r="J17" t="n">
         <v>398.13</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-29; 相对D0=1.73%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1672,24 +1456,6 @@
       <c r="J18" t="n">
         <v>955.3150000000001</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-29; 相对D0=-8.03%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1741,24 +1507,12 @@
       <c r="J19" s="4" t="n">
         <v>184.7651</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-29; 相对D0=3.01%; 历史重复2次; 重复日期=2026-05-26, 2026-05-28</t>
@@ -1810,24 +1564,12 @@
       <c r="J20" s="4" t="n">
         <v>312.4343</v>
       </c>
-      <c r="K20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-29; 相对D0=-4.20%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -1879,24 +1621,6 @@
       <c r="J21" t="n">
         <v>24.105</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-29; 相对D0=7.09%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1948,24 +1672,6 @@
       <c r="J22" t="n">
         <v>250.15</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-29; 相对D0=7.82%</t>
@@ -2017,24 +1723,6 @@
       <c r="J23" t="n">
         <v>149.22</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-29; 相对D0=14.34%</t>
@@ -2086,24 +1774,12 @@
       <c r="J24" s="4" t="n">
         <v>256.98</v>
       </c>
-      <c r="K24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-29; 相对D0=-2.01%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -2155,24 +1831,12 @@
       <c r="J25" s="4" t="n">
         <v>107.4</v>
       </c>
-      <c r="K25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-29; 相对D0=25.73%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2224,24 +1888,12 @@
       <c r="J26" s="4" t="n">
         <v>438.3</v>
       </c>
-      <c r="K26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-29; 相对D0=2.88%</t>
@@ -2293,24 +1945,12 @@
       <c r="J27" s="4" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="K27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-05-29; 相对D0=-6.51%</t>
@@ -2362,24 +2002,6 @@
       <c r="J28" t="n">
         <v>434.3</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-05-29; 相对D0=2.91%</t>
@@ -2431,24 +2053,6 @@
       <c r="J29" t="n">
         <v>88.53</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-05-29; 相对D0=2.36%</t>
@@ -2500,24 +2104,12 @@
       <c r="J30" s="4" t="n">
         <v>112.945</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-05-29; 相对D0=4.41%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2569,24 +2161,6 @@
       <c r="J31" t="n">
         <v>105.61</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-05-29; 相对D0=-0.26%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2638,24 +2212,12 @@
       <c r="J32" s="4" t="n">
         <v>383.08</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-05-29; 相对D0=-1.49%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2707,24 +2269,12 @@
       <c r="J33" s="4" t="n">
         <v>626.21</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-05-29; 相对D0=2.27%</t>
@@ -2776,24 +2326,12 @@
       <c r="J34" s="4" t="n">
         <v>68.63500000000001</v>
       </c>
-      <c r="K34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-05-29; 相对D0=-0.09%</t>
@@ -2845,24 +2383,6 @@
       <c r="J35" t="n">
         <v>106.57</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-05-29; 相对D0=-0.35%</t>
@@ -2914,24 +2434,12 @@
       <c r="J36" s="4" t="n">
         <v>12.8893</v>
       </c>
-      <c r="K36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-05-29; 相对D0=5.48%</t>
@@ -2983,24 +2491,6 @@
       <c r="J37" t="n">
         <v>83.7945</v>
       </c>
-      <c r="K37" t="n">
-        <v/>
-      </c>
-      <c r="L37" t="n">
-        <v/>
-      </c>
-      <c r="M37" t="n">
-        <v/>
-      </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
-      <c r="O37" t="n">
-        <v/>
-      </c>
-      <c r="P37" t="n">
-        <v/>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-05-29; 相对D0=-1.00%</t>
@@ -3052,24 +2542,12 @@
       <c r="J38" s="4" t="n">
         <v>18.18</v>
       </c>
-      <c r="K38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-05-29; 相对D0=-1.20%</t>
@@ -3121,24 +2599,6 @@
       <c r="J39" t="n">
         <v>310.425</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-05-29; 相对D0=-4.16%</t>
@@ -3190,24 +2650,12 @@
       <c r="J40" s="4" t="n">
         <v>271.27</v>
       </c>
-      <c r="K40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-05-29; 相对D0=-0.21%</t>
@@ -3259,24 +2707,6 @@
       <c r="J41" t="n">
         <v>90.95999999999999</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-05-29; 相对D0=0.10%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3328,24 +2758,6 @@
       <c r="J42" t="n">
         <v>35.96</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-05-29; 相对D0=-13.04%</t>
@@ -3397,24 +2809,12 @@
       <c r="J43" s="4" t="n">
         <v>123.9484</v>
       </c>
-      <c r="K43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-05-29; 相对D0=21.38%</t>
@@ -3466,24 +2866,6 @@
       <c r="J44" t="n">
         <v>222.98</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-05-29; 相对D0=16.77%</t>
@@ -3535,24 +2917,6 @@
       <c r="J45" t="n">
         <v>273.01</v>
       </c>
-      <c r="K45" t="n">
-        <v/>
-      </c>
-      <c r="L45" t="n">
-        <v/>
-      </c>
-      <c r="M45" t="n">
-        <v/>
-      </c>
-      <c r="N45" t="n">
-        <v/>
-      </c>
-      <c r="O45" t="n">
-        <v/>
-      </c>
-      <c r="P45" t="n">
-        <v/>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-05-29; 相对D0=-5.86%</t>
@@ -3604,24 +2968,12 @@
       <c r="J46" s="4" t="n">
         <v>728.36</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-05-29; 相对D0=8.55%</t>
@@ -3673,24 +3025,6 @@
       <c r="J47" t="n">
         <v>66.87</v>
       </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-05-29; 相对D0=-0.76%</t>
@@ -3742,24 +3076,6 @@
       <c r="J48" t="n">
         <v>1063.45</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-05-29; 相对D0=-0.56%</t>
@@ -3811,24 +3127,12 @@
       <c r="J49" s="4" t="n">
         <v>136.3199</v>
       </c>
-      <c r="K49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-05-29; 相对D0=5.10%</t>
@@ -3880,24 +3184,12 @@
       <c r="J50" s="4" t="n">
         <v>101.14</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-05-29; 相对D0=5.71%</t>
@@ -3949,24 +3241,12 @@
       <c r="J51" s="4" t="n">
         <v>443.58</v>
       </c>
-      <c r="K51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-05-29; 相对D0=3.89%</t>
@@ -4018,24 +3298,6 @@
       <c r="J52" t="n">
         <v>220.95</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-05-29; 相对D0=-2.38%</t>
@@ -4087,24 +3349,12 @@
       <c r="J53" s="4" t="n">
         <v>121.56</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-05-29; 相对D0=28.34%</t>
@@ -4156,24 +3406,12 @@
       <c r="J54" s="4" t="n">
         <v>276.95</v>
       </c>
-      <c r="K54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-05-29; 相对D0=7.44%</t>
@@ -4225,24 +3463,12 @@
       <c r="J55" s="4" t="n">
         <v>156.3</v>
       </c>
-      <c r="K55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-05-29; 相对D0=9.04%</t>
@@ -4479,24 +3705,12 @@
       <c r="J67" s="4" t="n">
         <v>92.935</v>
       </c>
-      <c r="K67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>D0=92.94; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -4548,24 +3762,12 @@
       <c r="J68" s="4" t="n">
         <v>68.7</v>
       </c>
-      <c r="K68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -4617,24 +3819,12 @@
       <c r="J69" s="4" t="n">
         <v>272.935</v>
       </c>
-      <c r="K69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>D0=272.94; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出)</t>
@@ -4686,24 +3876,12 @@
       <c r="J70" s="4" t="n">
         <v>170.18</v>
       </c>
-      <c r="K70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>D0=170.18; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -4755,24 +3933,12 @@
       <c r="J71" s="4" t="n">
         <v>345.755</v>
       </c>
-      <c r="K71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>D0=345.75; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出)</t>
@@ -4824,24 +3990,12 @@
       <c r="J72" s="4" t="n">
         <v>19.04</v>
       </c>
-      <c r="K72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>D0=19.04; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -4893,24 +4047,6 @@
       <c r="J73" t="n">
         <v>117.2</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=117.20; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -4962,24 +4098,6 @@
       <c r="J74" t="n">
         <v>134.84</v>
       </c>
-      <c r="K74" t="n">
-        <v/>
-      </c>
-      <c r="L74" t="n">
-        <v/>
-      </c>
-      <c r="M74" t="n">
-        <v/>
-      </c>
-      <c r="N74" t="n">
-        <v/>
-      </c>
-      <c r="O74" t="n">
-        <v/>
-      </c>
-      <c r="P74" t="n">
-        <v/>
-      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>D0=134.84; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -5031,24 +4149,12 @@
       <c r="J75" s="4" t="n">
         <v>248.675</v>
       </c>
-      <c r="K75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P75" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>D0=248.68; 最新=2026-05-29; 相对D0=0.00%; 本次触发=2026-05-29(正式卖出)</t>
@@ -5100,24 +4206,12 @@
       <c r="J76" s="4" t="n">
         <v>38.855</v>
       </c>
-      <c r="K76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O76" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P76" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-29; 相对D0=-6.31%</t>
@@ -5169,24 +4263,6 @@
       <c r="J77" t="n">
         <v>90.95999999999999</v>
       </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-05-29; 相对D0=0.35%</t>
@@ -5238,24 +4314,12 @@
       <c r="J78" s="4" t="n">
         <v>182.2836</v>
       </c>
-      <c r="K78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-05-29; 相对D0=-1.31%</t>
@@ -5307,24 +4371,12 @@
       <c r="J79" s="4" t="n">
         <v>132.98</v>
       </c>
-      <c r="K79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-05-29; 相对D0=-2.36%</t>
@@ -5376,24 +4428,6 @@
       <c r="J80" t="n">
         <v>35.96</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-05-29; 相对D0=-4.39%</t>
@@ -5445,24 +4479,6 @@
       <c r="J81" t="n">
         <v>312.53</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-05-29; 相对D0=1.69%</t>
@@ -5514,24 +4530,12 @@
       <c r="J82" s="4" t="n">
         <v>56.5</v>
       </c>
-      <c r="K82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-05-29; 相对D0=-1.67%</t>
@@ -5583,24 +4587,12 @@
       <c r="J83" s="4" t="n">
         <v>12.19</v>
       </c>
-      <c r="K83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-05-29; 相对D0=-8.69%</t>
@@ -5652,24 +4644,12 @@
       <c r="J84" s="4" t="n">
         <v>54.96</v>
       </c>
-      <c r="K84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="4" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n"/>
+      <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-05-29; 相对D0=-2.73%</t>
@@ -5721,24 +4701,6 @@
       <c r="J85" t="n">
         <v>137.66</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-05-29; 相对D0=8.90%</t>
@@ -5790,24 +4752,12 @@
       <c r="J86" s="4" t="n">
         <v>103.6428</v>
       </c>
-      <c r="K86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="n"/>
+      <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-05-29; 相对D0=-10.42%</t>
@@ -5859,24 +4809,6 @@
       <c r="J87" t="n">
         <v>287.31</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-05-29; 相对D0=0.35%</t>
@@ -5928,24 +4860,12 @@
       <c r="J88" s="4" t="n">
         <v>176.41</v>
       </c>
-      <c r="K88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="4" t="n"/>
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="n"/>
+      <c r="P88" s="4" t="n"/>
       <c r="Q88" s="4" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-05-29; 相对D0=-3.59%</t>
@@ -5996,24 +4916,6 @@
       </c>
       <c r="J89" t="n">
         <v>477.16</v>
-      </c>
-      <c r="K89" t="n">
-        <v/>
-      </c>
-      <c r="L89" t="n">
-        <v/>
-      </c>
-      <c r="M89" t="n">
-        <v/>
-      </c>
-      <c r="N89" t="n">
-        <v/>
-      </c>
-      <c r="O89" t="n">
-        <v/>
-      </c>
-      <c r="P89" t="n">
-        <v/>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -6111,7 +5013,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6123,7 +5024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6668,10 +5569,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6683,7 +5580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -6967,7 +5864,6 @@
       <c r="G9" s="13" t="n">
         <v>0.038853</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6999,7 +5895,6 @@
       <c r="G10" s="12" t="n">
         <v>-0.023814</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7429,9 +6324,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7443,7 +6335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7511,7 +6403,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -7881,7 +6773,6 @@
       <c r="E22" t="n">
         <v>134.84</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7999,7 +6890,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8247,7 +7137,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -9685,8 +8575,6 @@
       <c r="T19" t="b">
         <v>1</v>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.62; 4H分金=49.29</t>
@@ -10490,7 +9378,6 @@
           <t>HG1!</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>98 TradingView导入</t>
@@ -11156,8 +10043,6 @@
       <c r="T36" t="b">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=49.32; 4H分金=51.43</t>
@@ -11674,8 +10559,6 @@
       <c r="T42" t="b">
         <v>1</v>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.56; 4H分金=46.68</t>
@@ -11888,7 +10771,6 @@
       <c r="D3" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46170</v>
       </c>
@@ -11994,7 +10876,6 @@
       <c r="D5" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="8" t="n">
         <v>46164</v>
       </c>
@@ -12200,7 +11081,6 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" s="8" t="n">
         <v>46171</v>
       </c>
@@ -12312,7 +11192,6 @@
       <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" s="8" t="n">
         <v>46169</v>
       </c>
@@ -12401,7 +11280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12921,7 +11800,6 @@
       <c r="M10" s="12" t="n">
         <v>-0.058349</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -13241,7 +12119,6 @@
       <c r="M16" s="13" t="n">
         <v>0.078233</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13291,7 +12168,6 @@
       <c r="M17" s="13" t="n">
         <v>0.143448</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -13449,7 +12325,6 @@
       <c r="M20" s="13" t="n">
         <v>0.028849</v>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -13763,11 +12638,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13779,7 +12649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -13940,24 +12810,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14009,24 +12867,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14078,24 +12924,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14147,24 +12981,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14216,24 +13038,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14285,24 +13089,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14354,24 +13146,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14423,24 +13203,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14492,24 +13254,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14561,24 +13311,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14630,24 +13368,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14699,24 +13425,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14768,24 +13482,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14837,24 +13533,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14906,24 +13584,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -14975,24 +13635,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15044,24 +13692,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15113,24 +13749,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15182,24 +13800,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15436,24 +14042,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -15498,11 +14092,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15514,7 +14103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -15686,7 +14275,6 @@
       <c r="K4" s="13" t="n">
         <v>0.029122</v>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -16034,7 +14622,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -16122,7 +14710,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -16190,7 +14778,6 @@
       <c r="K15" s="12" t="n">
         <v>-0.009989</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -16278,7 +14865,6 @@
       <c r="K17" s="12" t="n">
         <v>-0.041632</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -16838,7 +15424,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
